--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/10-provisao-de-impostos.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/10-provisao-de-impostos.xlsx
@@ -1123,22 +1123,22 @@
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="15">
         <f>INDEX(B9:B20,Config!$B$7)</f>
-        <v>21570</v>
+        <v>21920</v>
       </c>
       <c r="B5" s="8" t="n"/>
       <c r="C5" s="16">
         <f>INDEX(F9:F20,Config!$B$7)</f>
-        <v>4334.7</v>
+        <v>4373.2</v>
       </c>
       <c r="D5" s="10" t="n"/>
       <c r="E5" s="17">
         <f>INDEX(J9:J20,Config!$B$7)</f>
-        <v>21937.07</v>
+        <v>21900.37</v>
       </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="18">
         <f>INDEX(K9:K20,Config!$B$7)</f>
-        <v>2372.7</v>
+        <v>2411.2</v>
       </c>
       <c r="H5" s="14" t="n"/>
       <c r="I5" s="17">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="B11" s="23">
         <f>'Entradas e pagamentos'!B7</f>
-        <v>47880</v>
+        <v>48330</v>
       </c>
       <c r="C11" s="23">
         <f>B11*Config!$B$8</f>
-        <v>5266.8</v>
+        <v>5316.3</v>
       </c>
       <c r="D11" s="23">
         <f>Config!$E$24</f>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="F11" s="24">
         <f>SUM(C11:E11)</f>
-        <v>7228.8</v>
+        <v>7278.3</v>
       </c>
       <c r="G11" s="23">
         <f>'Entradas e pagamentos'!F7</f>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="H11" s="23">
         <f>SUM($F$9:F11)</f>
-        <v>17539.95</v>
+        <v>17589.45</v>
       </c>
       <c r="I11" s="23">
         <f>SUM($G$9:G11)</f>
@@ -1378,11 +1378,11 @@
       </c>
       <c r="J11" s="24">
         <f>H11-I11</f>
-        <v>7522.95</v>
+        <v>7572.45</v>
       </c>
       <c r="K11" s="23">
         <f>C11+IF(MOD(3,12)+1=MATCH(Config!$B$11,Config!$H$5:$H$16,0),Config!$E$25,0)+IF(MOD(3,12)+1=MATCH(Config!$B$12,Config!$H$5:$H$16,0),Config!$F$25,0)</f>
-        <v>5266.8</v>
+        <v>5316.3</v>
       </c>
       <c r="L11" s="25" t="str">
         <f>IF(J11&lt;K11,"Falta separar","Coberto")</f>
@@ -1401,11 +1401,11 @@
       </c>
       <c r="B12" s="23">
         <f>'Entradas e pagamentos'!B8</f>
-        <v>38970</v>
+        <v>38935</v>
       </c>
       <c r="C12" s="23">
         <f>B12*Config!$B$8</f>
-        <v>4286.7</v>
+        <v>4282.85</v>
       </c>
       <c r="D12" s="23">
         <f>Config!$E$24</f>
@@ -1417,27 +1417,27 @@
       </c>
       <c r="F12" s="24">
         <f>SUM(C12:E12)</f>
-        <v>6248.7</v>
+        <v>6244.85</v>
       </c>
       <c r="G12" s="23">
         <f>'Entradas e pagamentos'!F8</f>
-        <v>5267</v>
+        <v>5316</v>
       </c>
       <c r="H12" s="23">
         <f>SUM($F$9:F12)</f>
-        <v>23788.65</v>
+        <v>23834.3</v>
       </c>
       <c r="I12" s="23">
         <f>SUM($G$9:G12)</f>
-        <v>15284</v>
+        <v>15333</v>
       </c>
       <c r="J12" s="24">
         <f>H12-I12</f>
-        <v>8504.65</v>
+        <v>8501.3</v>
       </c>
       <c r="K12" s="23">
         <f>C12+IF(MOD(4,12)+1=MATCH(Config!$B$11,Config!$H$5:$H$16,0),Config!$E$25,0)+IF(MOD(4,12)+1=MATCH(Config!$B$12,Config!$H$5:$H$16,0),Config!$F$25,0)</f>
-        <v>4286.7</v>
+        <v>4282.85</v>
       </c>
       <c r="L12" s="25" t="str">
         <f>IF(J12&lt;K12,"Falta separar","Coberto")</f>
@@ -1456,11 +1456,11 @@
       </c>
       <c r="B13" s="23">
         <f>'Entradas e pagamentos'!B9</f>
-        <v>44760</v>
+        <v>44745</v>
       </c>
       <c r="C13" s="23">
         <f>B13*Config!$B$8</f>
-        <v>4923.6</v>
+        <v>4921.95</v>
       </c>
       <c r="D13" s="23">
         <f>Config!$E$24</f>
@@ -1472,27 +1472,27 @@
       </c>
       <c r="F13" s="24">
         <f>SUM(C13:E13)</f>
-        <v>6885.6</v>
+        <v>6883.95</v>
       </c>
       <c r="G13" s="23">
         <f>'Entradas e pagamentos'!F9</f>
-        <v>4287</v>
+        <v>4283</v>
       </c>
       <c r="H13" s="23">
         <f>SUM($F$9:F13)</f>
-        <v>30674.25</v>
+        <v>30718.25</v>
       </c>
       <c r="I13" s="23">
         <f>SUM($G$9:G13)</f>
-        <v>19571</v>
+        <v>19616</v>
       </c>
       <c r="J13" s="24">
         <f>H13-I13</f>
-        <v>11103.25</v>
+        <v>11102.25</v>
       </c>
       <c r="K13" s="23">
         <f>C13+IF(MOD(5,12)+1=MATCH(Config!$B$11,Config!$H$5:$H$16,0),Config!$E$25,0)+IF(MOD(5,12)+1=MATCH(Config!$B$12,Config!$H$5:$H$16,0),Config!$F$25,0)</f>
-        <v>4923.6</v>
+        <v>4921.95</v>
       </c>
       <c r="L13" s="25" t="str">
         <f>IF(J13&lt;K13,"Falta separar","Coberto")</f>
@@ -1511,11 +1511,11 @@
       </c>
       <c r="B14" s="23">
         <f>'Entradas e pagamentos'!B10</f>
-        <v>43855</v>
+        <v>44160</v>
       </c>
       <c r="C14" s="23">
         <f>B14*Config!$B$8</f>
-        <v>4824.05</v>
+        <v>4857.6</v>
       </c>
       <c r="D14" s="23">
         <f>Config!$E$24</f>
@@ -1527,27 +1527,27 @@
       </c>
       <c r="F14" s="24">
         <f>SUM(C14:E14)</f>
-        <v>6786.05</v>
+        <v>6819.6</v>
       </c>
       <c r="G14" s="23">
         <f>'Entradas e pagamentos'!F10</f>
-        <v>4924</v>
+        <v>4922</v>
       </c>
       <c r="H14" s="23">
         <f>SUM($F$9:F14)</f>
-        <v>37460.3</v>
+        <v>37537.85</v>
       </c>
       <c r="I14" s="23">
         <f>SUM($G$9:G14)</f>
-        <v>24495</v>
+        <v>24538</v>
       </c>
       <c r="J14" s="24">
         <f>H14-I14</f>
-        <v>12965.3</v>
+        <v>12999.85</v>
       </c>
       <c r="K14" s="23">
         <f>C14+IF(MOD(6,12)+1=MATCH(Config!$B$11,Config!$H$5:$H$16,0),Config!$E$25,0)+IF(MOD(6,12)+1=MATCH(Config!$B$12,Config!$H$5:$H$16,0),Config!$F$25,0)</f>
-        <v>4824.05</v>
+        <v>4857.6</v>
       </c>
       <c r="L14" s="25" t="str">
         <f>IF(J14&lt;K14,"Falta separar","Coberto")</f>
@@ -1566,11 +1566,11 @@
       </c>
       <c r="B15" s="23">
         <f>'Entradas e pagamentos'!B11</f>
-        <v>53101</v>
+        <v>53461</v>
       </c>
       <c r="C15" s="23">
         <f>B15*Config!$B$8</f>
-        <v>5841.11</v>
+        <v>5880.71</v>
       </c>
       <c r="D15" s="23">
         <f>Config!$E$24</f>
@@ -1582,27 +1582,27 @@
       </c>
       <c r="F15" s="24">
         <f>SUM(C15:E15)</f>
-        <v>7803.11</v>
+        <v>7842.71</v>
       </c>
       <c r="G15" s="23">
         <f>'Entradas e pagamentos'!F11</f>
-        <v>4824</v>
+        <v>4858</v>
       </c>
       <c r="H15" s="23">
         <f>SUM($F$9:F15)</f>
-        <v>45263.41</v>
+        <v>45380.56</v>
       </c>
       <c r="I15" s="23">
         <f>SUM($G$9:G15)</f>
-        <v>29319</v>
+        <v>29396</v>
       </c>
       <c r="J15" s="24">
         <f>H15-I15</f>
-        <v>15944.41</v>
+        <v>15984.56</v>
       </c>
       <c r="K15" s="23">
         <f>C15+IF(MOD(7,12)+1=MATCH(Config!$B$11,Config!$H$5:$H$16,0),Config!$E$25,0)+IF(MOD(7,12)+1=MATCH(Config!$B$12,Config!$H$5:$H$16,0),Config!$F$25,0)</f>
-        <v>5841.11</v>
+        <v>5880.71</v>
       </c>
       <c r="L15" s="25" t="str">
         <f>IF(J15&lt;K15,"Falta separar","Coberto")</f>
@@ -1621,11 +1621,11 @@
       </c>
       <c r="B16" s="23">
         <f>'Entradas e pagamentos'!B12</f>
-        <v>50336</v>
+        <v>49651</v>
       </c>
       <c r="C16" s="23">
         <f>B16*Config!$B$8</f>
-        <v>5536.96</v>
+        <v>5461.61</v>
       </c>
       <c r="D16" s="23">
         <f>Config!$E$24</f>
@@ -1637,27 +1637,27 @@
       </c>
       <c r="F16" s="24">
         <f>SUM(C16:E16)</f>
-        <v>7498.96</v>
+        <v>7423.61</v>
       </c>
       <c r="G16" s="23">
         <f>'Entradas e pagamentos'!F12</f>
-        <v>5841</v>
+        <v>5881</v>
       </c>
       <c r="H16" s="23">
         <f>SUM($F$9:F16)</f>
-        <v>52762.37</v>
+        <v>52804.17</v>
       </c>
       <c r="I16" s="23">
         <f>SUM($G$9:G16)</f>
-        <v>35160</v>
+        <v>35277</v>
       </c>
       <c r="J16" s="24">
         <f>H16-I16</f>
-        <v>17602.37</v>
+        <v>17527.17</v>
       </c>
       <c r="K16" s="23">
         <f>C16+IF(MOD(8,12)+1=MATCH(Config!$B$11,Config!$H$5:$H$16,0),Config!$E$25,0)+IF(MOD(8,12)+1=MATCH(Config!$B$12,Config!$H$5:$H$16,0),Config!$F$25,0)</f>
-        <v>5536.96</v>
+        <v>5461.61</v>
       </c>
       <c r="L16" s="25" t="str">
         <f>IF(J16&lt;K16,"Falta separar","Coberto")</f>
@@ -1676,11 +1676,11 @@
       </c>
       <c r="B17" s="23">
         <f>'Entradas e pagamentos'!B13</f>
-        <v>21570</v>
+        <v>21920</v>
       </c>
       <c r="C17" s="23">
         <f>B17*Config!$B$8</f>
-        <v>2372.7</v>
+        <v>2411.2</v>
       </c>
       <c r="D17" s="23">
         <f>Config!$E$24</f>
@@ -1692,7 +1692,7 @@
       </c>
       <c r="F17" s="24">
         <f>SUM(C17:E17)</f>
-        <v>4334.7</v>
+        <v>4373.2</v>
       </c>
       <c r="G17" s="23">
         <f>'Entradas e pagamentos'!F13</f>
@@ -1700,19 +1700,19 @@
       </c>
       <c r="H17" s="23">
         <f>SUM($F$9:F17)</f>
-        <v>57097.07</v>
+        <v>57177.37</v>
       </c>
       <c r="I17" s="23">
         <f>SUM($G$9:G17)</f>
-        <v>35160</v>
+        <v>35277</v>
       </c>
       <c r="J17" s="24">
         <f>H17-I17</f>
-        <v>21937.07</v>
+        <v>21900.37</v>
       </c>
       <c r="K17" s="23">
         <f>C17+IF(MOD(9,12)+1=MATCH(Config!$B$11,Config!$H$5:$H$16,0),Config!$E$25,0)+IF(MOD(9,12)+1=MATCH(Config!$B$12,Config!$H$5:$H$16,0),Config!$F$25,0)</f>
-        <v>2372.7</v>
+        <v>2411.2</v>
       </c>
       <c r="L17" s="25" t="str">
         <f>IF(J17&lt;K17,"Falta separar","Coberto")</f>
@@ -1755,15 +1755,15 @@
       </c>
       <c r="H18" s="23">
         <f>SUM($F$9:F18)</f>
-        <v>59059.07</v>
+        <v>59139.37</v>
       </c>
       <c r="I18" s="23">
         <f>SUM($G$9:G18)</f>
-        <v>35160</v>
+        <v>35277</v>
       </c>
       <c r="J18" s="24">
         <f>H18-I18</f>
-        <v>23899.07</v>
+        <v>23862.37</v>
       </c>
       <c r="K18" s="23">
         <f>C18+IF(MOD(10,12)+1=MATCH(Config!$B$11,Config!$H$5:$H$16,0),Config!$E$25,0)+IF(MOD(10,12)+1=MATCH(Config!$B$12,Config!$H$5:$H$16,0),Config!$F$25,0)</f>
@@ -1810,15 +1810,15 @@
       </c>
       <c r="H19" s="23">
         <f>SUM($F$9:F19)</f>
-        <v>61021.07</v>
+        <v>61101.37</v>
       </c>
       <c r="I19" s="23">
         <f>SUM($G$9:G19)</f>
-        <v>35160</v>
+        <v>35277</v>
       </c>
       <c r="J19" s="24">
         <f>H19-I19</f>
-        <v>25861.07</v>
+        <v>25824.37</v>
       </c>
       <c r="K19" s="23">
         <f>C19+IF(MOD(11,12)+1=MATCH(Config!$B$11,Config!$H$5:$H$16,0),Config!$E$25,0)+IF(MOD(11,12)+1=MATCH(Config!$B$12,Config!$H$5:$H$16,0),Config!$F$25,0)</f>
@@ -1865,15 +1865,15 @@
       </c>
       <c r="H20" s="23">
         <f>SUM($F$9:F20)</f>
-        <v>62983.07</v>
+        <v>63063.37</v>
       </c>
       <c r="I20" s="23">
         <f>SUM($G$9:G20)</f>
-        <v>35160</v>
+        <v>35277</v>
       </c>
       <c r="J20" s="24">
         <f>H20-I20</f>
-        <v>27823.07</v>
+        <v>27786.37</v>
       </c>
       <c r="K20" s="23">
         <f>C20+IF(MOD(12,12)+1=MATCH(Config!$B$11,Config!$H$5:$H$16,0),Config!$E$25,0)+IF(MOD(12,12)+1=MATCH(Config!$B$12,Config!$H$5:$H$16,0),Config!$F$25,0)</f>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="B7" s="33" t="n">
-        <v>47880</v>
+        <v>48330</v>
       </c>
       <c r="C7" s="33" t="n">
         <v>2727</v>
@@ -2574,16 +2574,16 @@
         </is>
       </c>
       <c r="B8" s="33" t="n">
-        <v>38970</v>
+        <v>38935</v>
       </c>
       <c r="C8" s="33" t="n">
-        <v>5267</v>
+        <v>5316</v>
       </c>
       <c r="D8" s="33" t="n"/>
       <c r="E8" s="33" t="n"/>
       <c r="F8" s="34">
         <f>SUM(C8:E8)</f>
-        <v>5267</v>
+        <v>5316</v>
       </c>
     </row>
     <row r="9">
@@ -2593,16 +2593,16 @@
         </is>
       </c>
       <c r="B9" s="33" t="n">
-        <v>44760</v>
+        <v>44745</v>
       </c>
       <c r="C9" s="33" t="n">
-        <v>4287</v>
+        <v>4283</v>
       </c>
       <c r="D9" s="33" t="n"/>
       <c r="E9" s="33" t="n"/>
       <c r="F9" s="34">
         <f>SUM(C9:E9)</f>
-        <v>4287</v>
+        <v>4283</v>
       </c>
     </row>
     <row r="10">
@@ -2612,16 +2612,16 @@
         </is>
       </c>
       <c r="B10" s="33" t="n">
-        <v>43855</v>
+        <v>44160</v>
       </c>
       <c r="C10" s="33" t="n">
-        <v>4924</v>
+        <v>4922</v>
       </c>
       <c r="D10" s="33" t="n"/>
       <c r="E10" s="33" t="n"/>
       <c r="F10" s="34">
         <f>SUM(C10:E10)</f>
-        <v>4924</v>
+        <v>4922</v>
       </c>
     </row>
     <row r="11">
@@ -2631,16 +2631,16 @@
         </is>
       </c>
       <c r="B11" s="33" t="n">
-        <v>53101</v>
+        <v>53461</v>
       </c>
       <c r="C11" s="33" t="n">
-        <v>4824</v>
+        <v>4858</v>
       </c>
       <c r="D11" s="33" t="n"/>
       <c r="E11" s="33" t="n"/>
       <c r="F11" s="34">
         <f>SUM(C11:E11)</f>
-        <v>4824</v>
+        <v>4858</v>
       </c>
     </row>
     <row r="12">
@@ -2650,16 +2650,16 @@
         </is>
       </c>
       <c r="B12" s="33" t="n">
-        <v>50336</v>
+        <v>49651</v>
       </c>
       <c r="C12" s="33" t="n">
-        <v>5841</v>
+        <v>5881</v>
       </c>
       <c r="D12" s="33" t="n"/>
       <c r="E12" s="33" t="n"/>
       <c r="F12" s="34">
         <f>SUM(C12:E12)</f>
-        <v>5841</v>
+        <v>5881</v>
       </c>
     </row>
     <row r="13">
@@ -2669,7 +2669,7 @@
         </is>
       </c>
       <c r="B13" s="33" t="n">
-        <v>21570</v>
+        <v>21920</v>
       </c>
       <c r="C13" s="33" t="n"/>
       <c r="D13" s="33" t="n"/>
@@ -2732,11 +2732,11 @@
       </c>
       <c r="B17" s="36">
         <f>SUM(B5:B16)</f>
-        <v>358537</v>
+        <v>359267</v>
       </c>
       <c r="C17" s="36">
         <f>SUM(C5:C16)</f>
-        <v>35160</v>
+        <v>35277</v>
       </c>
       <c r="D17" s="36">
         <f>SUM(D5:D16)</f>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="F17" s="36">
         <f>SUM(F5:F16)</f>
-        <v>35160</v>
+        <v>35277</v>
       </c>
     </row>
     <row r="19">

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/10-provisao-de-impostos.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/10-provisao-de-impostos.xlsx
@@ -848,7 +848,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1021,17 +1021,29 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Clínica Vida Plena é uma clínica fictícia. Pacientes, convênios, nomes, contatos e valores são inventados; não há nenhum dado clínico. Apague o exemplo antes de começar. Agenda futura e vencimentos em aberto do exemplo são relativos a hoje.</t>
+          <t>Clínica Vida Plena é uma clínica fictícia. Pacientes, convênios, nomes, contatos e valores são inventados; não há nenhum dado clínico. Apague o exemplo antes de começar.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="46" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
+          <t>Data de referência</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os seus dados, troque a data de referência em Config por =HOJE(): daí em diante ela acompanha o dia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="46" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
           <t>Suporte</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>suporte@seusociogestor.com.br · resposta em até 5 dias úteis · reembolso em até 7 dias pelo mesmo canal.</t>
         </is>
@@ -1123,22 +1135,22 @@
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="15">
         <f>INDEX(B9:B20,Config!$B$7)</f>
-        <v>21920</v>
+        <v>20710</v>
       </c>
       <c r="B5" s="8" t="n"/>
       <c r="C5" s="16">
         <f>INDEX(F9:F20,Config!$B$7)</f>
-        <v>4373.2</v>
+        <v>4240.1</v>
       </c>
       <c r="D5" s="10" t="n"/>
       <c r="E5" s="17">
         <f>INDEX(J9:J20,Config!$B$7)</f>
-        <v>21900.37</v>
+        <v>22448.67</v>
       </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="18">
         <f>INDEX(K9:K20,Config!$B$7)</f>
-        <v>2411.2</v>
+        <v>2278.1</v>
       </c>
       <c r="H5" s="14" t="n"/>
       <c r="I5" s="17">
@@ -1236,11 +1248,11 @@
       </c>
       <c r="B9" s="23">
         <f>'Entradas e pagamentos'!B5</f>
-        <v>33270</v>
+        <v>25310</v>
       </c>
       <c r="C9" s="23">
         <f>B9*Config!$B$8</f>
-        <v>3659.7</v>
+        <v>2784.1</v>
       </c>
       <c r="D9" s="23">
         <f>Config!$E$24</f>
@@ -1252,7 +1264,7 @@
       </c>
       <c r="F9" s="24">
         <f>SUM(C9:E9)</f>
-        <v>5621.7</v>
+        <v>4746.1</v>
       </c>
       <c r="G9" s="23">
         <f>'Entradas e pagamentos'!F5</f>
@@ -1260,7 +1272,7 @@
       </c>
       <c r="H9" s="23">
         <f>SUM($F$9:F9)</f>
-        <v>5621.7</v>
+        <v>4746.1</v>
       </c>
       <c r="I9" s="23">
         <f>SUM($G$9:G9)</f>
@@ -1268,11 +1280,11 @@
       </c>
       <c r="J9" s="24">
         <f>H9-I9</f>
-        <v>1991.7</v>
+        <v>1116.1</v>
       </c>
       <c r="K9" s="23">
         <f>C9+IF(MOD(1,12)+1=MATCH(Config!$B$11,Config!$H$5:$H$16,0),Config!$E$25,0)+IF(MOD(1,12)+1=MATCH(Config!$B$12,Config!$H$5:$H$16,0),Config!$F$25,0)</f>
-        <v>3659.7</v>
+        <v>2784.1</v>
       </c>
       <c r="L9" s="25" t="str">
         <f>IF(J9&lt;K9,"Falta separar","Coberto")</f>
@@ -1291,11 +1303,11 @@
       </c>
       <c r="B10" s="23">
         <f>'Entradas e pagamentos'!B6</f>
-        <v>24795</v>
+        <v>25650</v>
       </c>
       <c r="C10" s="23">
         <f>B10*Config!$B$8</f>
-        <v>2727.45</v>
+        <v>2821.5</v>
       </c>
       <c r="D10" s="23">
         <f>Config!$E$24</f>
@@ -1307,27 +1319,27 @@
       </c>
       <c r="F10" s="24">
         <f>SUM(C10:E10)</f>
-        <v>4689.45</v>
+        <v>4783.5</v>
       </c>
       <c r="G10" s="23">
         <f>'Entradas e pagamentos'!F6</f>
-        <v>3660</v>
+        <v>2784</v>
       </c>
       <c r="H10" s="23">
         <f>SUM($F$9:F10)</f>
-        <v>10311.15</v>
+        <v>9529.6</v>
       </c>
       <c r="I10" s="23">
         <f>SUM($G$9:G10)</f>
-        <v>7290</v>
+        <v>6414</v>
       </c>
       <c r="J10" s="24">
         <f>H10-I10</f>
-        <v>3021.15</v>
+        <v>3115.6</v>
       </c>
       <c r="K10" s="23">
         <f>C10+IF(MOD(2,12)+1=MATCH(Config!$B$11,Config!$H$5:$H$16,0),Config!$E$25,0)+IF(MOD(2,12)+1=MATCH(Config!$B$12,Config!$H$5:$H$16,0),Config!$F$25,0)</f>
-        <v>2727.45</v>
+        <v>2821.5</v>
       </c>
       <c r="L10" s="25" t="str">
         <f>IF(J10&lt;K10,"Falta separar","Coberto")</f>
@@ -1346,11 +1358,11 @@
       </c>
       <c r="B11" s="23">
         <f>'Entradas e pagamentos'!B7</f>
-        <v>48330</v>
+        <v>40540</v>
       </c>
       <c r="C11" s="23">
         <f>B11*Config!$B$8</f>
-        <v>5316.3</v>
+        <v>4459.4</v>
       </c>
       <c r="D11" s="23">
         <f>Config!$E$24</f>
@@ -1362,27 +1374,27 @@
       </c>
       <c r="F11" s="24">
         <f>SUM(C11:E11)</f>
-        <v>7278.3</v>
+        <v>6421.4</v>
       </c>
       <c r="G11" s="23">
         <f>'Entradas e pagamentos'!F7</f>
-        <v>2727</v>
+        <v>2822</v>
       </c>
       <c r="H11" s="23">
         <f>SUM($F$9:F11)</f>
-        <v>17589.45</v>
+        <v>15951</v>
       </c>
       <c r="I11" s="23">
         <f>SUM($G$9:G11)</f>
-        <v>10017</v>
+        <v>9236</v>
       </c>
       <c r="J11" s="24">
         <f>H11-I11</f>
-        <v>7572.45</v>
+        <v>6715</v>
       </c>
       <c r="K11" s="23">
         <f>C11+IF(MOD(3,12)+1=MATCH(Config!$B$11,Config!$H$5:$H$16,0),Config!$E$25,0)+IF(MOD(3,12)+1=MATCH(Config!$B$12,Config!$H$5:$H$16,0),Config!$F$25,0)</f>
-        <v>5316.3</v>
+        <v>4459.4</v>
       </c>
       <c r="L11" s="25" t="str">
         <f>IF(J11&lt;K11,"Falta separar","Coberto")</f>
@@ -1401,11 +1413,11 @@
       </c>
       <c r="B12" s="23">
         <f>'Entradas e pagamentos'!B8</f>
-        <v>38935</v>
+        <v>40155</v>
       </c>
       <c r="C12" s="23">
         <f>B12*Config!$B$8</f>
-        <v>4282.85</v>
+        <v>4417.05</v>
       </c>
       <c r="D12" s="23">
         <f>Config!$E$24</f>
@@ -1417,27 +1429,27 @@
       </c>
       <c r="F12" s="24">
         <f>SUM(C12:E12)</f>
-        <v>6244.85</v>
+        <v>6379.05</v>
       </c>
       <c r="G12" s="23">
         <f>'Entradas e pagamentos'!F8</f>
-        <v>5316</v>
+        <v>4459</v>
       </c>
       <c r="H12" s="23">
         <f>SUM($F$9:F12)</f>
-        <v>23834.3</v>
+        <v>22330.05</v>
       </c>
       <c r="I12" s="23">
         <f>SUM($G$9:G12)</f>
-        <v>15333</v>
+        <v>13695</v>
       </c>
       <c r="J12" s="24">
         <f>H12-I12</f>
-        <v>8501.3</v>
+        <v>8635.05</v>
       </c>
       <c r="K12" s="23">
         <f>C12+IF(MOD(4,12)+1=MATCH(Config!$B$11,Config!$H$5:$H$16,0),Config!$E$25,0)+IF(MOD(4,12)+1=MATCH(Config!$B$12,Config!$H$5:$H$16,0),Config!$F$25,0)</f>
-        <v>4282.85</v>
+        <v>4417.05</v>
       </c>
       <c r="L12" s="25" t="str">
         <f>IF(J12&lt;K12,"Falta separar","Coberto")</f>
@@ -1456,11 +1468,11 @@
       </c>
       <c r="B13" s="23">
         <f>'Entradas e pagamentos'!B9</f>
-        <v>44745</v>
+        <v>45380</v>
       </c>
       <c r="C13" s="23">
         <f>B13*Config!$B$8</f>
-        <v>4921.95</v>
+        <v>4991.8</v>
       </c>
       <c r="D13" s="23">
         <f>Config!$E$24</f>
@@ -1472,27 +1484,27 @@
       </c>
       <c r="F13" s="24">
         <f>SUM(C13:E13)</f>
-        <v>6883.95</v>
+        <v>6953.8</v>
       </c>
       <c r="G13" s="23">
         <f>'Entradas e pagamentos'!F9</f>
-        <v>4283</v>
+        <v>4417</v>
       </c>
       <c r="H13" s="23">
         <f>SUM($F$9:F13)</f>
-        <v>30718.25</v>
+        <v>29283.85</v>
       </c>
       <c r="I13" s="23">
         <f>SUM($G$9:G13)</f>
-        <v>19616</v>
+        <v>18112</v>
       </c>
       <c r="J13" s="24">
         <f>H13-I13</f>
-        <v>11102.25</v>
+        <v>11171.85</v>
       </c>
       <c r="K13" s="23">
         <f>C13+IF(MOD(5,12)+1=MATCH(Config!$B$11,Config!$H$5:$H$16,0),Config!$E$25,0)+IF(MOD(5,12)+1=MATCH(Config!$B$12,Config!$H$5:$H$16,0),Config!$F$25,0)</f>
-        <v>4921.95</v>
+        <v>4991.8</v>
       </c>
       <c r="L13" s="25" t="str">
         <f>IF(J13&lt;K13,"Falta separar","Coberto")</f>
@@ -1511,11 +1523,11 @@
       </c>
       <c r="B14" s="23">
         <f>'Entradas e pagamentos'!B10</f>
-        <v>44160</v>
+        <v>47240</v>
       </c>
       <c r="C14" s="23">
         <f>B14*Config!$B$8</f>
-        <v>4857.6</v>
+        <v>5196.4</v>
       </c>
       <c r="D14" s="23">
         <f>Config!$E$24</f>
@@ -1527,27 +1539,27 @@
       </c>
       <c r="F14" s="24">
         <f>SUM(C14:E14)</f>
-        <v>6819.6</v>
+        <v>7158.4</v>
       </c>
       <c r="G14" s="23">
         <f>'Entradas e pagamentos'!F10</f>
-        <v>4922</v>
+        <v>4992</v>
       </c>
       <c r="H14" s="23">
         <f>SUM($F$9:F14)</f>
-        <v>37537.85</v>
+        <v>36442.25</v>
       </c>
       <c r="I14" s="23">
         <f>SUM($G$9:G14)</f>
-        <v>24538</v>
+        <v>23104</v>
       </c>
       <c r="J14" s="24">
         <f>H14-I14</f>
-        <v>12999.85</v>
+        <v>13338.25</v>
       </c>
       <c r="K14" s="23">
         <f>C14+IF(MOD(6,12)+1=MATCH(Config!$B$11,Config!$H$5:$H$16,0),Config!$E$25,0)+IF(MOD(6,12)+1=MATCH(Config!$B$12,Config!$H$5:$H$16,0),Config!$F$25,0)</f>
-        <v>4857.6</v>
+        <v>5196.4</v>
       </c>
       <c r="L14" s="25" t="str">
         <f>IF(J14&lt;K14,"Falta separar","Coberto")</f>
@@ -1566,11 +1578,11 @@
       </c>
       <c r="B15" s="23">
         <f>'Entradas e pagamentos'!B11</f>
-        <v>53461</v>
+        <v>44471</v>
       </c>
       <c r="C15" s="23">
         <f>B15*Config!$B$8</f>
-        <v>5880.71</v>
+        <v>4891.81</v>
       </c>
       <c r="D15" s="23">
         <f>Config!$E$24</f>
@@ -1582,27 +1594,27 @@
       </c>
       <c r="F15" s="24">
         <f>SUM(C15:E15)</f>
-        <v>7842.71</v>
+        <v>6853.81</v>
       </c>
       <c r="G15" s="23">
         <f>'Entradas e pagamentos'!F11</f>
-        <v>4858</v>
+        <v>5196</v>
       </c>
       <c r="H15" s="23">
         <f>SUM($F$9:F15)</f>
-        <v>45380.56</v>
+        <v>43296.06</v>
       </c>
       <c r="I15" s="23">
         <f>SUM($G$9:G15)</f>
-        <v>29396</v>
+        <v>28300</v>
       </c>
       <c r="J15" s="24">
         <f>H15-I15</f>
-        <v>15984.56</v>
+        <v>14996.06</v>
       </c>
       <c r="K15" s="23">
         <f>C15+IF(MOD(7,12)+1=MATCH(Config!$B$11,Config!$H$5:$H$16,0),Config!$E$25,0)+IF(MOD(7,12)+1=MATCH(Config!$B$12,Config!$H$5:$H$16,0),Config!$F$25,0)</f>
-        <v>5880.71</v>
+        <v>4891.81</v>
       </c>
       <c r="L15" s="25" t="str">
         <f>IF(J15&lt;K15,"Falta separar","Coberto")</f>
@@ -1621,11 +1633,11 @@
       </c>
       <c r="B16" s="23">
         <f>'Entradas e pagamentos'!B12</f>
-        <v>49651</v>
+        <v>55841</v>
       </c>
       <c r="C16" s="23">
         <f>B16*Config!$B$8</f>
-        <v>5461.61</v>
+        <v>6142.51</v>
       </c>
       <c r="D16" s="23">
         <f>Config!$E$24</f>
@@ -1637,27 +1649,27 @@
       </c>
       <c r="F16" s="24">
         <f>SUM(C16:E16)</f>
-        <v>7423.61</v>
+        <v>8104.51</v>
       </c>
       <c r="G16" s="23">
         <f>'Entradas e pagamentos'!F12</f>
-        <v>5881</v>
+        <v>4892</v>
       </c>
       <c r="H16" s="23">
         <f>SUM($F$9:F16)</f>
-        <v>52804.17</v>
+        <v>51400.57</v>
       </c>
       <c r="I16" s="23">
         <f>SUM($G$9:G16)</f>
-        <v>35277</v>
+        <v>33192</v>
       </c>
       <c r="J16" s="24">
         <f>H16-I16</f>
-        <v>17527.17</v>
+        <v>18208.57</v>
       </c>
       <c r="K16" s="23">
         <f>C16+IF(MOD(8,12)+1=MATCH(Config!$B$11,Config!$H$5:$H$16,0),Config!$E$25,0)+IF(MOD(8,12)+1=MATCH(Config!$B$12,Config!$H$5:$H$16,0),Config!$F$25,0)</f>
-        <v>5461.61</v>
+        <v>6142.51</v>
       </c>
       <c r="L16" s="25" t="str">
         <f>IF(J16&lt;K16,"Falta separar","Coberto")</f>
@@ -1676,11 +1688,11 @@
       </c>
       <c r="B17" s="23">
         <f>'Entradas e pagamentos'!B13</f>
-        <v>21920</v>
+        <v>20710</v>
       </c>
       <c r="C17" s="23">
         <f>B17*Config!$B$8</f>
-        <v>2411.2</v>
+        <v>2278.1</v>
       </c>
       <c r="D17" s="23">
         <f>Config!$E$24</f>
@@ -1692,7 +1704,7 @@
       </c>
       <c r="F17" s="24">
         <f>SUM(C17:E17)</f>
-        <v>4373.2</v>
+        <v>4240.1</v>
       </c>
       <c r="G17" s="23">
         <f>'Entradas e pagamentos'!F13</f>
@@ -1700,19 +1712,19 @@
       </c>
       <c r="H17" s="23">
         <f>SUM($F$9:F17)</f>
-        <v>57177.37</v>
+        <v>55640.67</v>
       </c>
       <c r="I17" s="23">
         <f>SUM($G$9:G17)</f>
-        <v>35277</v>
+        <v>33192</v>
       </c>
       <c r="J17" s="24">
         <f>H17-I17</f>
-        <v>21900.37</v>
+        <v>22448.67</v>
       </c>
       <c r="K17" s="23">
         <f>C17+IF(MOD(9,12)+1=MATCH(Config!$B$11,Config!$H$5:$H$16,0),Config!$E$25,0)+IF(MOD(9,12)+1=MATCH(Config!$B$12,Config!$H$5:$H$16,0),Config!$F$25,0)</f>
-        <v>2411.2</v>
+        <v>2278.1</v>
       </c>
       <c r="L17" s="25" t="str">
         <f>IF(J17&lt;K17,"Falta separar","Coberto")</f>
@@ -1755,15 +1767,15 @@
       </c>
       <c r="H18" s="23">
         <f>SUM($F$9:F18)</f>
-        <v>59139.37</v>
+        <v>57602.67</v>
       </c>
       <c r="I18" s="23">
         <f>SUM($G$9:G18)</f>
-        <v>35277</v>
+        <v>33192</v>
       </c>
       <c r="J18" s="24">
         <f>H18-I18</f>
-        <v>23862.37</v>
+        <v>24410.67</v>
       </c>
       <c r="K18" s="23">
         <f>C18+IF(MOD(10,12)+1=MATCH(Config!$B$11,Config!$H$5:$H$16,0),Config!$E$25,0)+IF(MOD(10,12)+1=MATCH(Config!$B$12,Config!$H$5:$H$16,0),Config!$F$25,0)</f>
@@ -1810,15 +1822,15 @@
       </c>
       <c r="H19" s="23">
         <f>SUM($F$9:F19)</f>
-        <v>61101.37</v>
+        <v>59564.67</v>
       </c>
       <c r="I19" s="23">
         <f>SUM($G$9:G19)</f>
-        <v>35277</v>
+        <v>33192</v>
       </c>
       <c r="J19" s="24">
         <f>H19-I19</f>
-        <v>25824.37</v>
+        <v>26372.67</v>
       </c>
       <c r="K19" s="23">
         <f>C19+IF(MOD(11,12)+1=MATCH(Config!$B$11,Config!$H$5:$H$16,0),Config!$E$25,0)+IF(MOD(11,12)+1=MATCH(Config!$B$12,Config!$H$5:$H$16,0),Config!$F$25,0)</f>
@@ -1865,15 +1877,15 @@
       </c>
       <c r="H20" s="23">
         <f>SUM($F$9:F20)</f>
-        <v>63063.37</v>
+        <v>61526.67</v>
       </c>
       <c r="I20" s="23">
         <f>SUM($G$9:G20)</f>
-        <v>35277</v>
+        <v>33192</v>
       </c>
       <c r="J20" s="24">
         <f>H20-I20</f>
-        <v>27786.37</v>
+        <v>28334.67</v>
       </c>
       <c r="K20" s="23">
         <f>C20+IF(MOD(12,12)+1=MATCH(Config!$B$11,Config!$H$5:$H$16,0),Config!$E$25,0)+IF(MOD(12,12)+1=MATCH(Config!$B$12,Config!$H$5:$H$16,0),Config!$F$25,0)</f>
@@ -2517,7 +2529,7 @@
         </is>
       </c>
       <c r="B5" s="33" t="n">
-        <v>33270</v>
+        <v>25310</v>
       </c>
       <c r="C5" s="33" t="n">
         <v>3630</v>
@@ -2536,16 +2548,16 @@
         </is>
       </c>
       <c r="B6" s="33" t="n">
-        <v>24795</v>
+        <v>25650</v>
       </c>
       <c r="C6" s="33" t="n">
-        <v>3660</v>
+        <v>2784</v>
       </c>
       <c r="D6" s="33" t="n"/>
       <c r="E6" s="33" t="n"/>
       <c r="F6" s="34">
         <f>SUM(C6:E6)</f>
-        <v>3660</v>
+        <v>2784</v>
       </c>
     </row>
     <row r="7">
@@ -2555,16 +2567,16 @@
         </is>
       </c>
       <c r="B7" s="33" t="n">
-        <v>48330</v>
+        <v>40540</v>
       </c>
       <c r="C7" s="33" t="n">
-        <v>2727</v>
+        <v>2822</v>
       </c>
       <c r="D7" s="33" t="n"/>
       <c r="E7" s="33" t="n"/>
       <c r="F7" s="34">
         <f>SUM(C7:E7)</f>
-        <v>2727</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="8">
@@ -2574,16 +2586,16 @@
         </is>
       </c>
       <c r="B8" s="33" t="n">
-        <v>38935</v>
+        <v>40155</v>
       </c>
       <c r="C8" s="33" t="n">
-        <v>5316</v>
+        <v>4459</v>
       </c>
       <c r="D8" s="33" t="n"/>
       <c r="E8" s="33" t="n"/>
       <c r="F8" s="34">
         <f>SUM(C8:E8)</f>
-        <v>5316</v>
+        <v>4459</v>
       </c>
     </row>
     <row r="9">
@@ -2593,16 +2605,16 @@
         </is>
       </c>
       <c r="B9" s="33" t="n">
-        <v>44745</v>
+        <v>45380</v>
       </c>
       <c r="C9" s="33" t="n">
-        <v>4283</v>
+        <v>4417</v>
       </c>
       <c r="D9" s="33" t="n"/>
       <c r="E9" s="33" t="n"/>
       <c r="F9" s="34">
         <f>SUM(C9:E9)</f>
-        <v>4283</v>
+        <v>4417</v>
       </c>
     </row>
     <row r="10">
@@ -2612,16 +2624,16 @@
         </is>
       </c>
       <c r="B10" s="33" t="n">
-        <v>44160</v>
+        <v>47240</v>
       </c>
       <c r="C10" s="33" t="n">
-        <v>4922</v>
+        <v>4992</v>
       </c>
       <c r="D10" s="33" t="n"/>
       <c r="E10" s="33" t="n"/>
       <c r="F10" s="34">
         <f>SUM(C10:E10)</f>
-        <v>4922</v>
+        <v>4992</v>
       </c>
     </row>
     <row r="11">
@@ -2631,16 +2643,16 @@
         </is>
       </c>
       <c r="B11" s="33" t="n">
-        <v>53461</v>
+        <v>44471</v>
       </c>
       <c r="C11" s="33" t="n">
-        <v>4858</v>
+        <v>5196</v>
       </c>
       <c r="D11" s="33" t="n"/>
       <c r="E11" s="33" t="n"/>
       <c r="F11" s="34">
         <f>SUM(C11:E11)</f>
-        <v>4858</v>
+        <v>5196</v>
       </c>
     </row>
     <row r="12">
@@ -2650,16 +2662,16 @@
         </is>
       </c>
       <c r="B12" s="33" t="n">
-        <v>49651</v>
+        <v>55841</v>
       </c>
       <c r="C12" s="33" t="n">
-        <v>5881</v>
+        <v>4892</v>
       </c>
       <c r="D12" s="33" t="n"/>
       <c r="E12" s="33" t="n"/>
       <c r="F12" s="34">
         <f>SUM(C12:E12)</f>
-        <v>5881</v>
+        <v>4892</v>
       </c>
     </row>
     <row r="13">
@@ -2669,7 +2681,7 @@
         </is>
       </c>
       <c r="B13" s="33" t="n">
-        <v>21920</v>
+        <v>20710</v>
       </c>
       <c r="C13" s="33" t="n"/>
       <c r="D13" s="33" t="n"/>
@@ -2732,11 +2744,11 @@
       </c>
       <c r="B17" s="36">
         <f>SUM(B5:B16)</f>
-        <v>359267</v>
+        <v>345297</v>
       </c>
       <c r="C17" s="36">
         <f>SUM(C5:C16)</f>
-        <v>35277</v>
+        <v>33192</v>
       </c>
       <c r="D17" s="36">
         <f>SUM(D5:D16)</f>
@@ -2748,7 +2760,7 @@
       </c>
       <c r="F17" s="36">
         <f>SUM(F5:F16)</f>
-        <v>35277</v>
+        <v>33192</v>
       </c>
     </row>
     <row r="19">

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/10-provisao-de-impostos.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/10-provisao-de-impostos.xlsx
@@ -1009,7 +1009,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores e gráficos funcionam.</t>
+          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores, semáforos e gráficos funcionam: as regras de cor que dependem do mês escolhido em Config usam INDIRECT, que é a forma que o Sheets aceita para regra condicional apontar para outra aba.</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os seus dados, troque a data de referência em Config por =HOJE(): daí em diante ela acompanha o dia.</t>
+          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os SEUS dados, troque em Config: a data de referência por =HOJE(), o ano, o mês do painel, o trimestre (onde houver) e a lista de feriados. Trocar só a data de referência deixa o resto apontando para 2026.</t>
         </is>
       </c>
     </row>
@@ -1954,7 +1954,7 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="A9:M20">
     <cfRule type="expression" priority="3" dxfId="2">
-      <formula>ROW()-9+1=Config!$B$7</formula>
+      <formula>ROW()-9+1=INDIRECT("Config!$B$7")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J9:J20">
